--- a/config/Anime.xlsx
+++ b/config/Anime.xlsx
@@ -69,7 +69,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="24">
   <si>
     <t>英雄编号</t>
   </si>
@@ -92,6 +92,9 @@
     <t>血量</t>
   </si>
   <si>
+    <t>攻击间隔</t>
+  </si>
+  <si>
     <t>id</t>
   </si>
   <si>
@@ -111,6 +114,9 @@
   </si>
   <si>
     <t>Hp</t>
+  </si>
+  <si>
+    <t>Cd</t>
   </si>
   <si>
     <t>number</t>
@@ -147,7 +153,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="23">
+  <fonts count="22">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -297,13 +303,6 @@
       <color theme="1"/>
       <name val="宋体"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -773,7 +772,7 @@
     <xf numFmtId="0" fontId="18" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyBorder="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyBorder="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1155,8 +1154,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G41"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="6"/>
+  <dimension ref="A1:H41"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="7"/>
   <cols>
     <col min="1" max="1" width="10.775" style="1" customWidth="1"/>
     <col min="2" max="3" width="9.10833333333333" style="1" customWidth="1"/>
@@ -1166,7 +1165,7 @@
     <col min="7" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:8">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -1188,54 +1187,63 @@
       <c r="G1" s="3" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="2" spans="1:7">
+      <c r="H1" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
       <c r="A2" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
+        <v>14</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
       <c r="A3" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
+        <v>16</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
       <c r="A4" s="1">
         <v>2001001</v>
       </c>
@@ -1246,10 +1254,10 @@
         <v>2</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F4" s="1">
         <v>1</v>
@@ -1257,8 +1265,11 @@
       <c r="G4" s="1">
         <v>10</v>
       </c>
-    </row>
-    <row r="5" spans="1:7">
+      <c r="H4" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
       <c r="A5" s="1">
         <v>2001002</v>
       </c>
@@ -1269,10 +1280,10 @@
         <v>2</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F5" s="1">
         <v>2</v>
@@ -1280,8 +1291,11 @@
       <c r="G5" s="1">
         <v>20</v>
       </c>
-    </row>
-    <row r="6" spans="1:7">
+      <c r="H5" s="1">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
       <c r="A6" s="1">
         <v>2001003</v>
       </c>
@@ -1292,10 +1306,10 @@
         <v>2</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F6" s="1">
         <v>3</v>
@@ -1303,8 +1317,11 @@
       <c r="G6" s="1">
         <v>30</v>
       </c>
-    </row>
-    <row r="7" spans="1:7">
+      <c r="H6" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
       <c r="A7" s="1">
         <v>2001004</v>
       </c>
@@ -1315,10 +1332,10 @@
         <v>2</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="F7" s="1">
         <v>4</v>
@@ -1326,8 +1343,11 @@
       <c r="G7" s="1">
         <v>40</v>
       </c>
-    </row>
-    <row r="8" spans="1:7">
+      <c r="H7" s="1">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
       <c r="A8" s="1">
         <v>2001005</v>
       </c>
@@ -1338,10 +1358,10 @@
         <v>2</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="F8" s="1">
         <v>5</v>
@@ -1349,8 +1369,11 @@
       <c r="G8" s="1">
         <v>50</v>
       </c>
-    </row>
-    <row r="9" spans="1:7">
+      <c r="H8" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
       <c r="A9" s="1">
         <v>2001006</v>
       </c>
@@ -1361,16 +1384,19 @@
         <v>2</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="F9" s="1">
         <v>6</v>
       </c>
       <c r="G9" s="1">
         <v>60</v>
+      </c>
+      <c r="H9" s="1">
+        <v>1.2</v>
       </c>
     </row>
     <row r="25" s="2" customFormat="1"/>
@@ -1394,6 +1420,14 @@
     <row r="41" s="2" customFormat="1"/>
   </sheetData>
   <conditionalFormatting sqref="D5:D6">
+    <cfRule type="expression" dxfId="0" priority="8">
+      <formula>CELL("row")=ROW()</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="1" priority="7">
+      <formula>AND(CELL("row")=ROW(),CELL("col")=COLUMN())</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D8:D9">
     <cfRule type="expression" dxfId="0" priority="6">
       <formula>CELL("row")=ROW()</formula>
     </cfRule>
@@ -1401,7 +1435,31 @@
       <formula>AND(CELL("row")=ROW(),CELL("col")=COLUMN())</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D8:D9">
+  <conditionalFormatting sqref="E5:E6">
+    <cfRule type="expression" dxfId="1" priority="47">
+      <formula>AND(CELL("row")=ROW(),CELL("col")=COLUMN())</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="0" priority="48">
+      <formula>CELL("row")=ROW()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E8:E9">
+    <cfRule type="expression" dxfId="1" priority="43">
+      <formula>AND(CELL("row")=ROW(),CELL("col")=COLUMN())</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="0" priority="44">
+      <formula>CELL("row")=ROW()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F1:F9">
+    <cfRule type="expression" dxfId="1" priority="9">
+      <formula>AND(CELL("row")=ROW(),CELL("col")=COLUMN())</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="0" priority="10">
+      <formula>CELL("row")=ROW()</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G1:G9">
     <cfRule type="expression" dxfId="0" priority="4">
       <formula>CELL("row")=ROW()</formula>
     </cfRule>
@@ -1409,31 +1467,7 @@
       <formula>AND(CELL("row")=ROW(),CELL("col")=COLUMN())</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E5:E6">
-    <cfRule type="expression" dxfId="1" priority="45">
-      <formula>AND(CELL("row")=ROW(),CELL("col")=COLUMN())</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="0" priority="46">
-      <formula>CELL("row")=ROW()</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E8:E9">
-    <cfRule type="expression" dxfId="1" priority="41">
-      <formula>AND(CELL("row")=ROW(),CELL("col")=COLUMN())</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="0" priority="42">
-      <formula>CELL("row")=ROW()</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F1:F9">
-    <cfRule type="expression" dxfId="1" priority="7">
-      <formula>AND(CELL("row")=ROW(),CELL("col")=COLUMN())</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="0" priority="8">
-      <formula>CELL("row")=ROW()</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G1:G9">
+  <conditionalFormatting sqref="H1:H9">
     <cfRule type="expression" dxfId="0" priority="2">
       <formula>CELL("row")=ROW()</formula>
     </cfRule>
@@ -1442,74 +1476,74 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D1:E3 $A63:$XFD1048576">
-    <cfRule type="expression" dxfId="1" priority="305">
+    <cfRule type="expression" dxfId="1" priority="307">
       <formula>AND(CELL("row")=ROW(),CELL("col")=COLUMN())</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="0" priority="306">
+    <cfRule type="expression" dxfId="0" priority="308">
       <formula>CELL("row")=ROW()</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A1:C5 H1:XFD5 A6:C9 H6:XFD9 A10:C62">
-    <cfRule type="expression" dxfId="1" priority="9">
+  <conditionalFormatting sqref="A1:C5 I1:XFD5 A6:C9 I6:XFD9 A10:C62">
+    <cfRule type="expression" dxfId="1" priority="11">
       <formula>AND(CELL("row")=ROW(),CELL("col")=COLUMN())</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="0" priority="10">
+    <cfRule type="expression" dxfId="0" priority="12">
       <formula>CELL("row")=ROW()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D10:E17">
-    <cfRule type="expression" dxfId="1" priority="257">
+    <cfRule type="expression" dxfId="1" priority="259">
       <formula>AND(CELL("row")=ROW(),CELL("col")=COLUMN())</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="0" priority="258">
+    <cfRule type="expression" dxfId="0" priority="260">
       <formula>CELL("row")=ROW()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F10:XFD62">
-    <cfRule type="expression" dxfId="1" priority="21">
+    <cfRule type="expression" dxfId="1" priority="23">
       <formula>AND(CELL("row")=ROW(),CELL("col")=COLUMN())</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="0" priority="22">
+    <cfRule type="expression" dxfId="0" priority="24">
       <formula>CELL("row")=ROW()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D19:E22">
-    <cfRule type="expression" dxfId="1" priority="245">
+    <cfRule type="expression" dxfId="1" priority="247">
       <formula>AND(CELL("row")=ROW(),CELL("col")=COLUMN())</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="0" priority="246">
+    <cfRule type="expression" dxfId="0" priority="248">
       <formula>CELL("row")=ROW()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D24:E25">
-    <cfRule type="expression" dxfId="1" priority="233">
+    <cfRule type="expression" dxfId="1" priority="235">
       <formula>AND(CELL("row")=ROW(),CELL("col")=COLUMN())</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="0" priority="234">
+    <cfRule type="expression" dxfId="0" priority="236">
       <formula>CELL("row")=ROW()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D27:E31">
-    <cfRule type="expression" dxfId="1" priority="211">
+    <cfRule type="expression" dxfId="1" priority="213">
       <formula>AND(CELL("row")=ROW(),CELL("col")=COLUMN())</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="0" priority="212">
+    <cfRule type="expression" dxfId="0" priority="214">
       <formula>CELL("row")=ROW()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D33:E57">
-    <cfRule type="expression" dxfId="1" priority="109">
+    <cfRule type="expression" dxfId="1" priority="111">
       <formula>AND(CELL("row")=ROW(),CELL("col")=COLUMN())</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="0" priority="110">
+    <cfRule type="expression" dxfId="0" priority="112">
       <formula>CELL("row")=ROW()</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D59:E62">
-    <cfRule type="expression" dxfId="1" priority="105">
+    <cfRule type="expression" dxfId="1" priority="107">
       <formula>AND(CELL("row")=ROW(),CELL("col")=COLUMN())</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="0" priority="106">
+    <cfRule type="expression" dxfId="0" priority="108">
       <formula>CELL("row")=ROW()</formula>
     </cfRule>
   </conditionalFormatting>
